--- a/LAHM/Rainier (UPS UPS UPS)/UPS metadata/Data 2021.xlsx
+++ b/LAHM/Rainier (UPS UPS UPS)/UPS metadata/Data 2021.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nesh/Documents/Repositories/LAI_in_snow/LAHM/Rainier (UPS UPS UPS)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nesh/Documents/Repositories/LAI_in_snow/LAHM/Rainier (UPS UPS UPS)/UPS metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{370955AC-B45E-D447-9788-5188D7558B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AE7993-98EF-B94D-82A0-80C1D1A23EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27720" windowHeight="15960" xr2:uid="{03D9CB5E-3EA5-49F8-AFE2-845958ADD9BC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="15900" windowHeight="15960" activeTab="3" xr2:uid="{03D9CB5E-3EA5-49F8-AFE2-845958ADD9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview-Concentrations" sheetId="4" r:id="rId1"/>
@@ -2111,9 +2111,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2231,25 +2234,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA9831A-9FB3-4F7A-AF72-8B1BA9F73088}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865A094C-55A3-4DA1-9A50-253B41A6ABD1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2271,9 +2264,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865A094C-55A3-4DA1-9A50-253B41A6ABD1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA9831A-9FB3-4F7A-AF72-8B1BA9F73088}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>